--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending4(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending4(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_结局4（下） (1)" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="366">
   <si>
     <t>ID</t>
   </si>
@@ -190,12 +190,6 @@
   </si>
   <si>
     <t>源类型=type:txt_DVABL; 层级=10</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_DVABL; 层级=11</t>
   </si>
   <si>
     <t>13</t>
@@ -465,12 +459,6 @@
     <t>源类型=type:txt_DVABL; 层级=39</t>
   </si>
   <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=40</t>
-  </si>
-  <si>
     <t>42</t>
   </si>
   <si>
@@ -618,7 +606,28 @@
     <t>57</t>
   </si>
   <si>
-    <t>达成结局——【恶魔的双翼】</t>
+    <r>
+      <t>达成结局</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>——</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【恶魔的双翼】</t>
+    </r>
+  </si>
+  <si>
+    <t>unlockending(Ending2)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=56</t>
@@ -2354,7 +2363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2823,12 +2832,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" ht="55.5" spans="1:12">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -2843,7 +2852,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -2858,12 +2867,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" ht="54" spans="1:12">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>25</v>
@@ -2881,7 +2890,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -2896,12 +2905,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" ht="54" spans="1:12">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" ht="40.5" spans="1:12">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
         <v>25</v>
@@ -2919,7 +2928,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -2934,15 +2943,15 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" ht="40.5" spans="1:12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" ht="55.5" spans="1:12">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
@@ -2957,7 +2966,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -2972,12 +2981,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" ht="55.5" spans="1:12">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -2995,7 +3004,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3010,206 +3019,206 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" ht="40.5" spans="1:12">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>68</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" ht="28.5" spans="1:12">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
         <v>13</v>
       </c>
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" t="s">
-        <v>67</v>
-      </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" ht="40.5" spans="1:12">
-      <c r="A19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" t="s">
+        <v>15</v>
+      </c>
+      <c r="L19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" ht="55.5" spans="1:12">
+      <c r="A20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" t="s">
         <v>25</v>
       </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" t="s">
-        <v>15</v>
-      </c>
-      <c r="K19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" ht="28.5" spans="1:12">
-      <c r="A20" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" t="s">
+        <v>15</v>
+      </c>
+      <c r="L20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" ht="40.5" spans="1:12">
+      <c r="A22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" ht="55.5" spans="1:12">
+      <c r="A23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" t="s">
         <v>13</v>
       </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" t="s">
-        <v>73</v>
-      </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" t="s">
-        <v>15</v>
-      </c>
-      <c r="K20" t="s">
-        <v>15</v>
-      </c>
-      <c r="L20" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" ht="55.5" spans="1:12">
-      <c r="A21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K21" t="s">
-        <v>15</v>
-      </c>
-      <c r="L21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" t="s">
-        <v>78</v>
-      </c>
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" t="s">
-        <v>79</v>
-      </c>
-      <c r="H22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" t="s">
-        <v>15</v>
-      </c>
-      <c r="K22" t="s">
-        <v>15</v>
-      </c>
-      <c r="L22" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" ht="40.5" spans="1:12">
-      <c r="A23" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" t="s">
-        <v>25</v>
-      </c>
       <c r="C23" t="s">
         <v>14</v>
       </c>
@@ -3223,7 +3232,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3238,15 +3247,15 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" ht="55.5" spans="1:12">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -3261,7 +3270,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3276,12 +3285,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" ht="55.5" spans="1:12">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" ht="40.5" spans="1:12">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
         <v>25</v>
@@ -3299,7 +3308,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3314,12 +3323,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" ht="40.5" spans="1:12">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s">
         <v>25</v>
@@ -3337,7 +3346,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3352,12 +3361,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" ht="40.5" spans="1:12">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" ht="42" spans="1:12">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
         <v>25</v>
@@ -3375,7 +3384,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3387,15 +3396,15 @@
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="L27" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" ht="42" spans="1:12">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" ht="43.5" spans="1:12">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B28" t="s">
         <v>25</v>
@@ -3413,7 +3422,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3425,15 +3434,15 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="29" ht="43.5" spans="1:12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" ht="75" spans="1:12">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
         <v>25</v>
@@ -3451,7 +3460,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3466,12 +3475,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" ht="75" spans="1:12">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
@@ -3489,7 +3498,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3504,12 +3513,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" ht="75" spans="1:12">
       <c r="A31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
@@ -3527,7 +3536,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3542,12 +3551,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="32" ht="75" spans="1:12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" ht="57" spans="1:12">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B32" t="s">
         <v>25</v>
@@ -3565,7 +3574,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3580,12 +3589,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" ht="57" spans="1:12">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" ht="28.5" spans="1:12">
       <c r="A33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s">
         <v>25</v>
@@ -3603,7 +3612,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3618,12 +3627,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" ht="28.5" spans="1:12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" ht="54" spans="1:12">
       <c r="A34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B34" t="s">
         <v>25</v>
@@ -3641,7 +3650,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3656,168 +3665,168 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35" ht="54" spans="1:12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s">
+        <v>120</v>
+      </c>
+      <c r="H35" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" t="s">
+        <v>15</v>
+      </c>
+      <c r="K35" t="s">
+        <v>15</v>
+      </c>
+      <c r="L35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" ht="27" spans="1:12">
+      <c r="A36" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" t="s">
         <v>25</v>
       </c>
-      <c r="C35" t="s">
-        <v>14</v>
-      </c>
-      <c r="D35" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" t="s">
-        <v>119</v>
-      </c>
-      <c r="H35" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" t="s">
-        <v>15</v>
-      </c>
-      <c r="K35" t="s">
-        <v>15</v>
-      </c>
-      <c r="L35" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
-      <c r="A36" t="s">
-        <v>121</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s">
+        <v>123</v>
+      </c>
+      <c r="H36" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" t="s">
+        <v>15</v>
+      </c>
+      <c r="K36" t="s">
+        <v>15</v>
+      </c>
+      <c r="L36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" ht="28.5" spans="1:12">
+      <c r="A37" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" t="s">
         <v>13</v>
       </c>
-      <c r="C36" t="s">
-        <v>14</v>
-      </c>
-      <c r="D36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" t="s">
-        <v>122</v>
-      </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" t="s">
-        <v>15</v>
-      </c>
-      <c r="K36" t="s">
-        <v>15</v>
-      </c>
-      <c r="L36" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" ht="27" spans="1:12">
-      <c r="A37" t="s">
-        <v>124</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s">
+        <v>126</v>
+      </c>
+      <c r="H37" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>15</v>
+      </c>
+      <c r="K37" t="s">
+        <v>15</v>
+      </c>
+      <c r="L37" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" ht="27" spans="1:12">
+      <c r="A38" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" t="s">
         <v>25</v>
       </c>
-      <c r="C37" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" t="s">
-        <v>125</v>
-      </c>
-      <c r="H37" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J37" t="s">
-        <v>15</v>
-      </c>
-      <c r="K37" t="s">
-        <v>15</v>
-      </c>
-      <c r="L37" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="38" ht="28.5" spans="1:12">
-      <c r="A38" t="s">
-        <v>127</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" t="s">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s">
+        <v>129</v>
+      </c>
+      <c r="H38" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38" t="s">
+        <v>15</v>
+      </c>
+      <c r="K38" t="s">
+        <v>18</v>
+      </c>
+      <c r="L38" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" ht="42" spans="1:12">
+      <c r="A39" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" t="s">
         <v>13</v>
       </c>
-      <c r="C38" t="s">
-        <v>14</v>
-      </c>
-      <c r="D38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" t="s">
-        <v>128</v>
-      </c>
-      <c r="H38" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" t="s">
-        <v>15</v>
-      </c>
-      <c r="J38" t="s">
-        <v>15</v>
-      </c>
-      <c r="K38" t="s">
-        <v>15</v>
-      </c>
-      <c r="L38" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="39" ht="27" spans="1:12">
-      <c r="A39" t="s">
-        <v>130</v>
-      </c>
-      <c r="B39" t="s">
-        <v>25</v>
-      </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
@@ -3831,7 +3840,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -3843,15 +3852,15 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="40" ht="42" spans="1:12">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" ht="28.5" spans="1:12">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -3869,7 +3878,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -3884,15 +3893,15 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="41" ht="28.5" spans="1:12">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="41" ht="54" spans="1:12">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -3907,7 +3916,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -3922,12 +3931,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="42" ht="28.5" spans="1:12">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" ht="40.5" spans="1:12">
       <c r="A42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B42" t="s">
         <v>25</v>
@@ -3945,7 +3954,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -3960,15 +3969,15 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="43" ht="54" spans="1:12">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" ht="42" spans="1:12">
       <c r="A43" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
@@ -3983,7 +3992,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -3998,12 +4007,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="44" ht="40.5" spans="1:12">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" ht="28.5" spans="1:12">
       <c r="A44" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B44" t="s">
         <v>25</v>
@@ -4021,7 +4030,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4036,12 +4045,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="45" ht="42" spans="1:12">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="45" ht="69" spans="1:12">
       <c r="A45" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4059,7 +4068,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4074,12 +4083,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="46" ht="28.5" spans="1:12">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="46" ht="27" spans="1:12">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B46" t="s">
         <v>25</v>
@@ -4097,7 +4106,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4112,12 +4121,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" ht="69" spans="1:12">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" ht="28.5" spans="1:12">
       <c r="A47" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4135,7 +4144,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4150,15 +4159,15 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="48" ht="27" spans="1:12">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" ht="42" spans="1:12">
       <c r="A48" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
@@ -4173,7 +4182,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4188,12 +4197,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="49" ht="28.5" spans="1:12">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4211,7 +4220,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4226,15 +4235,15 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="50" ht="42" spans="1:12">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
@@ -4249,7 +4258,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4264,12 +4273,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4287,7 +4296,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4302,12 +4311,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52" ht="30" spans="1:12">
       <c r="A52" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B52" t="s">
         <v>25</v>
@@ -4325,10 +4334,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>169</v>
-      </c>
-      <c r="H52" t="s">
-        <v>15</v>
+        <v>171</v>
       </c>
       <c r="I52" t="s">
         <v>15</v>
@@ -4337,18 +4343,18 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="L52" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="53" ht="54" spans="1:12">
       <c r="A53" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4363,7 +4369,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4375,15 +4381,15 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="L53" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="54" ht="30" spans="1:12">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="54" ht="40.5" spans="1:12">
       <c r="A54" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B54" t="s">
         <v>25</v>
@@ -4401,9 +4407,11 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>175</v>
-      </c>
-      <c r="H54"/>
+        <v>179</v>
+      </c>
+      <c r="H54" t="s">
+        <v>15</v>
+      </c>
       <c r="I54" t="s">
         <v>15</v>
       </c>
@@ -4411,15 +4419,15 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="55" ht="54" spans="1:12">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="55" ht="28.5" spans="1:12">
       <c r="A55" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B55" t="s">
         <v>25</v>
@@ -4437,7 +4445,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4449,15 +4457,15 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="L55" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="56" ht="40.5" spans="1:12">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B56" t="s">
         <v>25</v>
@@ -4474,8 +4482,8 @@
       <c r="F56" t="s">
         <v>15</v>
       </c>
-      <c r="G56" t="s">
-        <v>183</v>
+      <c r="G56" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4487,86 +4495,10 @@
         <v>15</v>
       </c>
       <c r="K56" t="s">
-        <v>15</v>
+        <v>187</v>
       </c>
       <c r="L56" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="57" ht="28.5" spans="1:12">
-      <c r="A57" t="s">
-        <v>185</v>
-      </c>
-      <c r="B57" t="s">
-        <v>25</v>
-      </c>
-      <c r="C57" t="s">
-        <v>14</v>
-      </c>
-      <c r="D57" t="s">
-        <v>15</v>
-      </c>
-      <c r="E57" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" t="s">
-        <v>186</v>
-      </c>
-      <c r="H57" t="s">
-        <v>15</v>
-      </c>
-      <c r="I57" t="s">
-        <v>15</v>
-      </c>
-      <c r="J57" t="s">
-        <v>15</v>
-      </c>
-      <c r="K57" t="s">
-        <v>187</v>
-      </c>
-      <c r="L57" t="s">
         <v>188</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12">
-      <c r="A58" t="s">
-        <v>189</v>
-      </c>
-      <c r="B58" t="s">
-        <v>25</v>
-      </c>
-      <c r="C58" t="s">
-        <v>14</v>
-      </c>
-      <c r="D58" t="s">
-        <v>15</v>
-      </c>
-      <c r="E58" t="s">
-        <v>15</v>
-      </c>
-      <c r="F58" t="s">
-        <v>15</v>
-      </c>
-      <c r="G58" t="s">
-        <v>190</v>
-      </c>
-      <c r="H58" t="s">
-        <v>15</v>
-      </c>
-      <c r="I58" t="s">
-        <v>15</v>
-      </c>
-      <c r="J58" t="s">
-        <v>15</v>
-      </c>
-      <c r="K58" t="s">
-        <v>15</v>
-      </c>
-      <c r="L58" t="s">
-        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -4587,122 +4519,122 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B11" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" t="s">
         <v>205</v>
-      </c>
-      <c r="B12" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B13" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B15" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -4724,616 +4656,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" t="s">
         <v>218</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>219</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>220</v>
-      </c>
-      <c r="D2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" t="s">
         <v>224</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>225</v>
-      </c>
-      <c r="D3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F3" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E4" t="s">
         <v>229</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>230</v>
-      </c>
-      <c r="D4" t="s">
-        <v>231</v>
-      </c>
-      <c r="E4" t="s">
-        <v>232</v>
-      </c>
-      <c r="F4" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E5" t="s">
         <v>234</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
         <v>235</v>
-      </c>
-      <c r="D5" t="s">
-        <v>236</v>
-      </c>
-      <c r="E5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F5" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E6" t="s">
         <v>239</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
         <v>240</v>
-      </c>
-      <c r="D6" t="s">
-        <v>241</v>
-      </c>
-      <c r="E6" t="s">
-        <v>242</v>
-      </c>
-      <c r="F6" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" t="s">
+        <v>242</v>
+      </c>
+      <c r="D7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E7" t="s">
         <v>244</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
         <v>245</v>
-      </c>
-      <c r="D7" t="s">
-        <v>246</v>
-      </c>
-      <c r="E7" t="s">
-        <v>247</v>
-      </c>
-      <c r="F7" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" t="s">
+        <v>248</v>
+      </c>
+      <c r="D8" t="s">
         <v>249</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
         <v>250</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
         <v>251</v>
-      </c>
-      <c r="D8" t="s">
-        <v>252</v>
-      </c>
-      <c r="E8" t="s">
-        <v>253</v>
-      </c>
-      <c r="F8" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B9" t="s">
+        <v>252</v>
+      </c>
+      <c r="C9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E9" t="s">
         <v>255</v>
       </c>
-      <c r="C9" t="s">
+      <c r="F9" t="s">
         <v>256</v>
-      </c>
-      <c r="D9" t="s">
-        <v>257</v>
-      </c>
-      <c r="E9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F9" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
+        <v>257</v>
+      </c>
+      <c r="B10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" t="s">
         <v>260</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E10" t="s">
         <v>261</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>262</v>
-      </c>
-      <c r="D10" t="s">
-        <v>263</v>
-      </c>
-      <c r="E10" t="s">
-        <v>264</v>
-      </c>
-      <c r="F10" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11" t="s">
+        <v>264</v>
+      </c>
+      <c r="D11" t="s">
+        <v>265</v>
+      </c>
+      <c r="E11" t="s">
         <v>266</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>267</v>
-      </c>
-      <c r="D11" t="s">
-        <v>268</v>
-      </c>
-      <c r="E11" t="s">
-        <v>269</v>
-      </c>
-      <c r="F11" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D12" t="s">
+        <v>270</v>
+      </c>
+      <c r="E12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" t="s">
         <v>272</v>
-      </c>
-      <c r="D12" t="s">
-        <v>273</v>
-      </c>
-      <c r="E12" t="s">
-        <v>274</v>
-      </c>
-      <c r="F12" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B13" t="s">
+        <v>273</v>
+      </c>
+      <c r="C13" t="s">
+        <v>274</v>
+      </c>
+      <c r="D13" t="s">
+        <v>275</v>
+      </c>
+      <c r="E13" t="s">
         <v>276</v>
       </c>
-      <c r="C13" t="s">
+      <c r="F13" t="s">
         <v>277</v>
-      </c>
-      <c r="D13" t="s">
-        <v>278</v>
-      </c>
-      <c r="E13" t="s">
-        <v>279</v>
-      </c>
-      <c r="F13" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B14" t="s">
+        <v>278</v>
+      </c>
+      <c r="C14" t="s">
+        <v>279</v>
+      </c>
+      <c r="D14" t="s">
+        <v>280</v>
+      </c>
+      <c r="E14" t="s">
         <v>281</v>
       </c>
-      <c r="C14" t="s">
+      <c r="F14" t="s">
         <v>282</v>
-      </c>
-      <c r="D14" t="s">
-        <v>283</v>
-      </c>
-      <c r="E14" t="s">
-        <v>284</v>
-      </c>
-      <c r="F14" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B15" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" t="s">
+        <v>284</v>
+      </c>
+      <c r="D15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E15" t="s">
         <v>286</v>
       </c>
-      <c r="C15" t="s">
+      <c r="F15" t="s">
         <v>287</v>
-      </c>
-      <c r="D15" t="s">
-        <v>288</v>
-      </c>
-      <c r="E15" t="s">
-        <v>289</v>
-      </c>
-      <c r="F15" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B16" t="s">
+        <v>288</v>
+      </c>
+      <c r="C16" t="s">
+        <v>289</v>
+      </c>
+      <c r="D16" t="s">
+        <v>290</v>
+      </c>
+      <c r="E16" t="s">
         <v>291</v>
       </c>
-      <c r="C16" t="s">
+      <c r="F16" t="s">
         <v>292</v>
-      </c>
-      <c r="D16" t="s">
-        <v>293</v>
-      </c>
-      <c r="E16" t="s">
-        <v>294</v>
-      </c>
-      <c r="F16" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B17" t="s">
+        <v>293</v>
+      </c>
+      <c r="C17" t="s">
+        <v>294</v>
+      </c>
+      <c r="D17" t="s">
+        <v>295</v>
+      </c>
+      <c r="E17" t="s">
         <v>296</v>
       </c>
-      <c r="C17" t="s">
+      <c r="F17" t="s">
         <v>297</v>
-      </c>
-      <c r="D17" t="s">
-        <v>298</v>
-      </c>
-      <c r="E17" t="s">
-        <v>299</v>
-      </c>
-      <c r="F17" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B18" t="s">
+        <v>298</v>
+      </c>
+      <c r="C18" t="s">
+        <v>299</v>
+      </c>
+      <c r="D18" t="s">
+        <v>300</v>
+      </c>
+      <c r="E18" t="s">
         <v>301</v>
       </c>
-      <c r="C18" t="s">
+      <c r="F18" t="s">
         <v>302</v>
-      </c>
-      <c r="D18" t="s">
-        <v>303</v>
-      </c>
-      <c r="E18" t="s">
-        <v>304</v>
-      </c>
-      <c r="F18" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B19" t="s">
+        <v>303</v>
+      </c>
+      <c r="C19" t="s">
+        <v>304</v>
+      </c>
+      <c r="D19" t="s">
+        <v>305</v>
+      </c>
+      <c r="E19" t="s">
         <v>306</v>
       </c>
-      <c r="C19" t="s">
+      <c r="F19" t="s">
         <v>307</v>
-      </c>
-      <c r="D19" t="s">
-        <v>308</v>
-      </c>
-      <c r="E19" t="s">
-        <v>309</v>
-      </c>
-      <c r="F19" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B20" t="s">
+        <v>308</v>
+      </c>
+      <c r="C20" t="s">
+        <v>309</v>
+      </c>
+      <c r="D20" t="s">
+        <v>310</v>
+      </c>
+      <c r="E20" t="s">
         <v>311</v>
       </c>
-      <c r="C20" t="s">
+      <c r="F20" t="s">
         <v>312</v>
-      </c>
-      <c r="D20" t="s">
-        <v>313</v>
-      </c>
-      <c r="E20" t="s">
-        <v>314</v>
-      </c>
-      <c r="F20" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B21" t="s">
+        <v>313</v>
+      </c>
+      <c r="C21" t="s">
+        <v>314</v>
+      </c>
+      <c r="D21" t="s">
+        <v>315</v>
+      </c>
+      <c r="E21" t="s">
         <v>316</v>
       </c>
-      <c r="C21" t="s">
+      <c r="F21" t="s">
         <v>317</v>
-      </c>
-      <c r="D21" t="s">
-        <v>318</v>
-      </c>
-      <c r="E21" t="s">
-        <v>319</v>
-      </c>
-      <c r="F21" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B22" t="s">
+        <v>318</v>
+      </c>
+      <c r="C22" t="s">
+        <v>319</v>
+      </c>
+      <c r="D22" t="s">
+        <v>320</v>
+      </c>
+      <c r="E22" t="s">
         <v>321</v>
       </c>
-      <c r="C22" t="s">
+      <c r="F22" t="s">
         <v>322</v>
-      </c>
-      <c r="D22" t="s">
-        <v>323</v>
-      </c>
-      <c r="E22" t="s">
-        <v>324</v>
-      </c>
-      <c r="F22" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B23" t="s">
+        <v>323</v>
+      </c>
+      <c r="C23" t="s">
+        <v>324</v>
+      </c>
+      <c r="D23" t="s">
+        <v>325</v>
+      </c>
+      <c r="E23" t="s">
         <v>326</v>
       </c>
-      <c r="C23" t="s">
+      <c r="F23" t="s">
         <v>327</v>
-      </c>
-      <c r="D23" t="s">
-        <v>328</v>
-      </c>
-      <c r="E23" t="s">
-        <v>329</v>
-      </c>
-      <c r="F23" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B24" t="s">
+        <v>328</v>
+      </c>
+      <c r="C24" t="s">
+        <v>329</v>
+      </c>
+      <c r="D24" t="s">
+        <v>270</v>
+      </c>
+      <c r="E24" t="s">
+        <v>330</v>
+      </c>
+      <c r="F24" t="s">
         <v>331</v>
-      </c>
-      <c r="C24" t="s">
-        <v>332</v>
-      </c>
-      <c r="D24" t="s">
-        <v>273</v>
-      </c>
-      <c r="E24" t="s">
-        <v>333</v>
-      </c>
-      <c r="F24" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
+        <v>332</v>
+      </c>
+      <c r="B25" t="s">
+        <v>333</v>
+      </c>
+      <c r="C25" t="s">
+        <v>334</v>
+      </c>
+      <c r="D25" t="s">
         <v>335</v>
       </c>
-      <c r="B25" t="s">
+      <c r="E25" t="s">
         <v>336</v>
       </c>
-      <c r="C25" t="s">
+      <c r="F25" t="s">
         <v>337</v>
-      </c>
-      <c r="D25" t="s">
-        <v>338</v>
-      </c>
-      <c r="E25" t="s">
-        <v>339</v>
-      </c>
-      <c r="F25" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B26" t="s">
+        <v>338</v>
+      </c>
+      <c r="C26" t="s">
+        <v>339</v>
+      </c>
+      <c r="D26" t="s">
+        <v>340</v>
+      </c>
+      <c r="E26" t="s">
         <v>341</v>
       </c>
-      <c r="C26" t="s">
+      <c r="F26" t="s">
         <v>342</v>
-      </c>
-      <c r="D26" t="s">
-        <v>343</v>
-      </c>
-      <c r="E26" t="s">
-        <v>344</v>
-      </c>
-      <c r="F26" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B27" t="s">
+        <v>343</v>
+      </c>
+      <c r="C27" t="s">
+        <v>344</v>
+      </c>
+      <c r="D27" t="s">
+        <v>345</v>
+      </c>
+      <c r="E27" t="s">
         <v>346</v>
       </c>
-      <c r="C27" t="s">
+      <c r="F27" t="s">
         <v>347</v>
-      </c>
-      <c r="D27" t="s">
-        <v>348</v>
-      </c>
-      <c r="E27" t="s">
-        <v>349</v>
-      </c>
-      <c r="F27" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B28" t="s">
+        <v>348</v>
+      </c>
+      <c r="C28" t="s">
+        <v>349</v>
+      </c>
+      <c r="D28" t="s">
+        <v>345</v>
+      </c>
+      <c r="E28" t="s">
+        <v>350</v>
+      </c>
+      <c r="F28" t="s">
         <v>351</v>
-      </c>
-      <c r="C28" t="s">
-        <v>352</v>
-      </c>
-      <c r="D28" t="s">
-        <v>348</v>
-      </c>
-      <c r="E28" t="s">
-        <v>353</v>
-      </c>
-      <c r="F28" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B29" t="s">
+        <v>352</v>
+      </c>
+      <c r="C29" t="s">
+        <v>353</v>
+      </c>
+      <c r="D29" t="s">
+        <v>354</v>
+      </c>
+      <c r="E29" t="s">
         <v>355</v>
       </c>
-      <c r="C29" t="s">
+      <c r="F29" t="s">
         <v>356</v>
-      </c>
-      <c r="D29" t="s">
-        <v>357</v>
-      </c>
-      <c r="E29" t="s">
-        <v>358</v>
-      </c>
-      <c r="F29" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B30" t="s">
+        <v>357</v>
+      </c>
+      <c r="C30" t="s">
+        <v>358</v>
+      </c>
+      <c r="D30" t="s">
+        <v>359</v>
+      </c>
+      <c r="E30" t="s">
         <v>360</v>
       </c>
-      <c r="C30" t="s">
+      <c r="F30" t="s">
         <v>361</v>
-      </c>
-      <c r="D30" t="s">
-        <v>362</v>
-      </c>
-      <c r="E30" t="s">
-        <v>363</v>
-      </c>
-      <c r="F30" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
+        <v>362</v>
+      </c>
+      <c r="B31" t="s">
+        <v>363</v>
+      </c>
+      <c r="C31" t="s">
+        <v>364</v>
+      </c>
+      <c r="D31" t="s">
         <v>365</v>
-      </c>
-      <c r="B31" t="s">
-        <v>366</v>
-      </c>
-      <c r="C31" t="s">
-        <v>367</v>
-      </c>
-      <c r="D31" t="s">
-        <v>368</v>
       </c>
     </row>
   </sheetData>
